--- a/ejemplos/vulnerabilidades_ejemplo.xlsx
+++ b/ejemplos/vulnerabilidades_ejemplo.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerabilidades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsables" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,7 +526,6 @@
           <t>srv-admin-01</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -591,7 +591,6 @@
           <t>srv-mail-01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -622,7 +621,6 @@
           <t>srv-web-02</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -688,7 +686,6 @@
           <t>srv-web-02</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -719,7 +716,6 @@
           <t>srv-mail-01</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -737,7 +733,6 @@
           <t>Escalamiento de privilegios local (EJEMPLO)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>7.8</v>
       </c>
@@ -781,7 +776,6 @@
           <t>srv-db-01</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -812,7 +806,6 @@
           <t>srv-web-01</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -878,7 +871,6 @@
           <t>srv-admin-01</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Cerrada</t>
@@ -901,18 +893,116 @@
           <t>Urgente-X</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>srv-api-01</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Abierta</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>srv-web-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ana Ejemplo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ana.ejemplo@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>srv-web-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ana Ejemplo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ana.ejemplo@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>srv-db-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bruno Ejemplo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bruno.ejemplo@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>srv-admin-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Carla Ejemplo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
